--- a/assets/plantillas/CONSTRUCCION.xlsx
+++ b/assets/plantillas/CONSTRUCCION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno Franco\Desktop\AppArq\appArquitectos\apparq\assets\plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno Franco\Desktop\AppArq\appArquitectos\assets\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA627CE2-056F-4EF5-BBBD-98F8A8D83D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA6E700-13C2-461E-A166-D8CBD1D0C0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>COSTO</t>
   </si>
@@ -84,9 +84,6 @@
     <t>COSTO TOTAL:</t>
   </si>
   <si>
-    <t>TOTAL:</t>
-  </si>
-  <si>
     <t>Indirectos de oficina</t>
   </si>
   <si>
@@ -106,13 +103,28 @@
   </si>
   <si>
     <t>COSTO DIRECTO:</t>
+  </si>
+  <si>
+    <t>SUBTOTAL 1</t>
+  </si>
+  <si>
+    <t>SUBTOTAL 2</t>
+  </si>
+  <si>
+    <t>SUBTOTAL 3</t>
+  </si>
+  <si>
+    <t>SUBTOTAL 4</t>
+  </si>
+  <si>
+    <t>TOTAL DE INDIRECTOS:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,6 +150,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -228,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -241,11 +259,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -256,16 +283,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -613,31 +648,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="14"/>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -661,13 +696,13 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
@@ -699,124 +734,188 @@
       <c r="B12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="A13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
       <c r="D16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F16" s="7"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="13"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="13"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="32">
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="A13:D13"/>
@@ -825,22 +924,6 @@
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A22:C22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="119" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
